--- a/artfynd/A 3041-2022 artfynd.xlsx
+++ b/artfynd/A 3041-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132085762</v>
       </c>
       <c r="B2" t="n">
-        <v>57894</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3041-2022 artfynd.xlsx
+++ b/artfynd/A 3041-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132085762</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3041-2022 artfynd.xlsx
+++ b/artfynd/A 3041-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132085762</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3041-2022 artfynd.xlsx
+++ b/artfynd/A 3041-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>132085762</v>
       </c>
       <c r="B2" t="n">
-        <v>57900</v>
+        <v>57921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -769,6 +769,1021 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132085894</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Granö, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>480381</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6253006</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Almundsryd</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132085748</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102637</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Granö, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>480459</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6253136</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Almundsryd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132085996</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96030</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2381</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bandpraktmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Plagiomnium elatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Granö, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>480786</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6253087</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Almundsryd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132085456</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96423</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Granö, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>480782</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6253080</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Almundsryd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132085892</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Granö, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>480783</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6253087</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Almundsryd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132085623</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106409</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Granö, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>480792</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6253078</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Almundsryd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Två plantor</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132085704</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103764</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Granö, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>480770</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6253085</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Almundsryd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132085600</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99857</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222308</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rankstarr</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carex elongata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Granö, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>480766</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6253102</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Almundsryd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132085694</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Granö, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>480503</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6253138</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Almundsryd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132085758</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Granö, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>480783</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6253077</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Almundsryd</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Naturvärdesinventering (NVI)</t>
         </is>

--- a/artfynd/A 3041-2022 artfynd.xlsx
+++ b/artfynd/A 3041-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085996</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085456</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085762</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085892</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085894</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085623</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085704</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085748</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085600</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085694</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,8 +1843,26 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085758</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>